--- a/outputs/32023.xlsx
+++ b/outputs/32023.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="32">
   <si>
     <t xml:space="preserve">Employee Name</t>
   </si>
@@ -214,40 +214,44 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -503,691 +507,675 @@
   <dimension ref="A1:L19"/>
   <sheetFormatPr defaultColWidth="8.84375" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.38"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="17.31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="13.84"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="0" width="12.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="13.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="12.31"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="15.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="13.69"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="16" style="0" width="10.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="14.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="13.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="17.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="13.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="12.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="13.15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="12.31"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="15.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="13.69"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="16" style="1" width="10.69"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="2" t="s">
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
+      <c r="G1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1" s="2" t="s">
+      <c r="I1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="L1" s="2" t="s">
+      <c r="K1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L1" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="0" t="str">
-        <f aca="false">IF($C$3&lt;$E4,"C74",IF($C$3&lt;$G4,"C75",IF($C$3&lt;$I4,"C76",IF($C$3&lt;$K4,"C77","C78"))))</f>
-        <v>C78</v>
-      </c>
-      <c r="D2" s="1" t="s">
+      <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" s="4" t="n">
         <v>19.24</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="3" t="n">
+      <c r="G2" s="4" t="n">
         <v>21.62</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="3" t="n">
+      <c r="I2" s="4" t="n">
         <v>24</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="3" t="n">
+      <c r="K2" s="4" t="n">
         <v>28.2</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="L2" s="5" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="0" t="str">
-        <f aca="false">IF($C$3&lt;$E5,"C74",IF($C$3&lt;$G5,"C75",IF($C$3&lt;$I5,"C76",IF($C$3&lt;$K5,"C77","C78"))))</f>
-        <v>C78</v>
-      </c>
-      <c r="C3" s="5" t="n">
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="6" t="n">
         <f aca="true">TODAY()</f>
-        <v>46270</v>
-      </c>
-      <c r="D3" s="6" t="s">
+        <v>46271</v>
+      </c>
+      <c r="D3" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="I3" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="J3" s="8" t="s">
+      <c r="J3" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="K3" s="7"/>
-      <c r="L3" s="8" t="s">
+      <c r="K3" s="8"/>
+      <c r="L3" s="9" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
+      <c r="A4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="0" t="str">
-        <f aca="false">IF($C$3&lt;$E6,"C74",IF($C$3&lt;$G6,"C75",IF($C$3&lt;$I6,"C76",IF($C$3&lt;$K6,"C77","C78"))))</f>
-        <v>C78</v>
-      </c>
-      <c r="D4" s="5" t="n">
+      <c r="B4" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="6" t="n">
         <v>42132</v>
       </c>
-      <c r="E4" s="5" t="n">
+      <c r="E4" s="6" t="n">
         <v>42498</v>
       </c>
-      <c r="F4" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="G4" s="5" t="n">
+      <c r="F4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G4" s="6" t="n">
         <v>42863</v>
       </c>
-      <c r="H4" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="I4" s="5" t="n">
+      <c r="H4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I4" s="6" t="n">
         <v>43228</v>
       </c>
-      <c r="J4" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="K4" s="5" t="n">
+      <c r="J4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K4" s="6" t="n">
         <v>43618</v>
       </c>
-      <c r="L4" s="0" t="s">
+      <c r="L4" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
+      <c r="A5" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="0" t="str">
-        <f aca="false">IF($C$3&lt;$E7,"C74",IF($C$3&lt;$G7,"C75",IF($C$3&lt;$I7,"C76",IF($C$3&lt;$K7,"C77","C78"))))</f>
-        <v>C78</v>
-      </c>
-      <c r="D5" s="5" t="n">
+      <c r="B5" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="6" t="n">
         <v>42143</v>
       </c>
-      <c r="E5" s="5" t="n">
+      <c r="E5" s="6" t="n">
         <v>42509</v>
       </c>
-      <c r="F5" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="G5" s="5" t="n">
+      <c r="F5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G5" s="6" t="n">
         <v>42874</v>
       </c>
-      <c r="H5" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="I5" s="5" t="n">
+      <c r="H5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I5" s="6" t="n">
         <v>43239</v>
       </c>
-      <c r="J5" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="K5" s="5" t="n">
+      <c r="J5" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K5" s="6" t="n">
         <v>43618</v>
       </c>
-      <c r="L5" s="0" t="s">
+      <c r="L5" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
+      <c r="A6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="0" t="str">
-        <f aca="false">IF($C$3&lt;$E8,"C74",IF($C$3&lt;$G8,"C75",IF($C$3&lt;$I8,"C76",IF($C$3&lt;$K8,"C77","C78"))))</f>
-        <v>C78</v>
-      </c>
-      <c r="D6" s="5" t="n">
+      <c r="B6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="6" t="n">
         <v>42194</v>
       </c>
-      <c r="E6" s="5" t="n">
+      <c r="E6" s="6" t="n">
         <v>42560</v>
       </c>
-      <c r="F6" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="G6" s="5" t="n">
+      <c r="F6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G6" s="6" t="n">
         <v>42925</v>
       </c>
-      <c r="H6" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="I6" s="5" t="n">
+      <c r="H6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I6" s="6" t="n">
         <v>43290</v>
       </c>
-      <c r="J6" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="K6" s="5" t="n">
+      <c r="J6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K6" s="6" t="n">
         <v>43655</v>
       </c>
-      <c r="L6" s="0" t="s">
+      <c r="L6" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
+      <c r="A7" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="0" t="str">
-        <f aca="false">IF($C$3&lt;$E9,"C74",IF($C$3&lt;$G9,"C75",IF($C$3&lt;$I9,"C76",IF($C$3&lt;$K9,"C77","C78"))))</f>
-        <v>C78</v>
-      </c>
-      <c r="D7" s="5" t="n">
+      <c r="B7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="6" t="n">
         <v>42316</v>
       </c>
-      <c r="E7" s="5" t="n">
+      <c r="E7" s="6" t="n">
         <v>42682</v>
       </c>
-      <c r="F7" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="G7" s="5" t="n">
+      <c r="F7" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G7" s="6" t="n">
         <v>43047</v>
       </c>
-      <c r="H7" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="I7" s="5" t="n">
+      <c r="H7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I7" s="6" t="n">
         <v>43412</v>
       </c>
-      <c r="J7" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="K7" s="5" t="n">
+      <c r="J7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K7" s="6" t="n">
         <v>43777</v>
       </c>
-      <c r="L7" s="0" t="s">
+      <c r="L7" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="A8" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="0" t="str">
-        <f aca="false">IF($C$3&lt;$E10,"C74",IF($C$3&lt;$G10,"C75",IF($C$3&lt;$I10,"C76",IF($C$3&lt;$K10,"C77","C78"))))</f>
-        <v>C78</v>
-      </c>
-      <c r="D8" s="5" t="n">
+      <c r="B8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="6" t="n">
         <v>42624</v>
       </c>
-      <c r="E8" s="5" t="n">
+      <c r="E8" s="6" t="n">
         <v>42989</v>
       </c>
-      <c r="F8" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="G8" s="5" t="n">
+      <c r="F8" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G8" s="6" t="n">
         <v>43354</v>
       </c>
-      <c r="H8" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="I8" s="5" t="n">
+      <c r="H8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I8" s="6" t="n">
         <v>43719</v>
       </c>
-      <c r="J8" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="K8" s="5" t="n">
+      <c r="J8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K8" s="6" t="n">
         <v>44085</v>
       </c>
-      <c r="L8" s="0" t="s">
+      <c r="L8" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="A9" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="0" t="str">
-        <f aca="false">IF($C$3&lt;$E11,"C74",IF($C$3&lt;$G11,"C75",IF($C$3&lt;$I11,"C76",IF($C$3&lt;$K11,"C77","C78"))))</f>
-        <v>C78</v>
-      </c>
-      <c r="D9" s="5" t="n">
+      <c r="B9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="6" t="n">
         <v>42624</v>
       </c>
-      <c r="E9" s="5" t="n">
+      <c r="E9" s="6" t="n">
         <v>42989</v>
       </c>
-      <c r="F9" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="G9" s="5" t="n">
+      <c r="F9" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G9" s="6" t="n">
         <v>43354</v>
       </c>
-      <c r="H9" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="I9" s="5" t="n">
+      <c r="H9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I9" s="6" t="n">
         <v>43719</v>
       </c>
-      <c r="J9" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="K9" s="5" t="n">
+      <c r="J9" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K9" s="6" t="n">
         <v>44085</v>
       </c>
-      <c r="L9" s="0" t="s">
+      <c r="L9" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+      <c r="A10" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="0" t="str">
-        <f aca="false">IF($C$3&lt;$E12,"C74",IF($C$3&lt;$G12,"C75",IF($C$3&lt;$I12,"C76",IF($C$3&lt;$K12,"C77","C78"))))</f>
-        <v>C78</v>
-      </c>
-      <c r="D10" s="5" t="n">
+      <c r="B10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="6" t="n">
         <v>42722</v>
       </c>
-      <c r="E10" s="5" t="n">
+      <c r="E10" s="6" t="n">
         <v>43087</v>
       </c>
-      <c r="F10" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="G10" s="5" t="n">
+      <c r="F10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G10" s="6" t="n">
         <v>43452</v>
       </c>
-      <c r="H10" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="I10" s="5" t="n">
+      <c r="H10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I10" s="6" t="n">
         <v>43817</v>
       </c>
-      <c r="J10" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="K10" s="5" t="n">
+      <c r="J10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K10" s="6" t="n">
         <v>44183</v>
       </c>
-      <c r="L10" s="0" t="s">
+      <c r="L10" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="A11" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="0" t="str">
-        <f aca="false">IF($C$3&lt;$E13,"C74",IF($C$3&lt;$G13,"C75",IF($C$3&lt;$I13,"C76",IF($C$3&lt;$K13,"C77","C78"))))</f>
-        <v>C78</v>
-      </c>
-      <c r="D11" s="5" t="n">
+      <c r="B11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="6" t="n">
         <v>42624</v>
       </c>
-      <c r="E11" s="5" t="n">
+      <c r="E11" s="6" t="n">
         <v>42989</v>
       </c>
-      <c r="F11" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="G11" s="5" t="n">
+      <c r="F11" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G11" s="6" t="n">
         <v>43354</v>
       </c>
-      <c r="H11" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="I11" s="5" t="n">
+      <c r="H11" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I11" s="6" t="n">
         <v>43719</v>
       </c>
-      <c r="J11" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="K11" s="5" t="n">
+      <c r="J11" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K11" s="6" t="n">
         <v>44085</v>
       </c>
-      <c r="L11" s="0" t="s">
+      <c r="L11" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
+      <c r="A12" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="0" t="str">
-        <f aca="false">IF($C$3&lt;$E14,"C74",IF($C$3&lt;$G14,"C75",IF($C$3&lt;$I14,"C76",IF($C$3&lt;$K14,"C77","C78"))))</f>
-        <v>C78</v>
-      </c>
-      <c r="D12" s="5" t="n">
+      <c r="B12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="6" t="n">
         <v>42722</v>
       </c>
-      <c r="E12" s="5" t="n">
+      <c r="E12" s="6" t="n">
         <v>43087</v>
       </c>
-      <c r="F12" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="G12" s="5" t="n">
+      <c r="F12" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G12" s="6" t="n">
         <v>43452</v>
       </c>
-      <c r="H12" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="I12" s="5" t="n">
+      <c r="H12" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I12" s="6" t="n">
         <v>43817</v>
       </c>
-      <c r="J12" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="K12" s="5" t="n">
+      <c r="J12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K12" s="6" t="n">
         <v>44183</v>
       </c>
-      <c r="L12" s="0" t="s">
+      <c r="L12" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
+      <c r="A13" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="0" t="str">
-        <f aca="false">IF($C$3&lt;$E15,"C74",IF($C$3&lt;$G15,"C75",IF($C$3&lt;$I15,"C76",IF($C$3&lt;$K15,"C77","C78"))))</f>
-        <v>C78</v>
-      </c>
-      <c r="D13" s="5" t="n">
+      <c r="B13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="6" t="n">
         <v>43709</v>
       </c>
-      <c r="E13" s="5" t="n">
+      <c r="E13" s="6" t="n">
         <v>44075</v>
       </c>
-      <c r="F13" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="G13" s="5" t="n">
+      <c r="F13" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G13" s="6" t="n">
         <v>44440</v>
       </c>
-      <c r="H13" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="I13" s="5" t="n">
+      <c r="H13" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I13" s="6" t="n">
         <v>44805</v>
       </c>
-      <c r="J13" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="K13" s="5" t="n">
+      <c r="J13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K13" s="6" t="n">
         <v>45170</v>
       </c>
-      <c r="L13" s="0" t="s">
+      <c r="L13" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
+      <c r="A14" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="0" t="str">
-        <f aca="false">IF($C$3&lt;$E16,"C74",IF($C$3&lt;$G16,"C75",IF($C$3&lt;$I16,"C76",IF($C$3&lt;$K16,"C77","C78"))))</f>
-        <v>C78</v>
-      </c>
-      <c r="D14" s="5" t="n">
+      <c r="B14" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D14" s="6" t="n">
         <v>43836</v>
       </c>
-      <c r="E14" s="5" t="n">
+      <c r="E14" s="6" t="n">
         <v>44202</v>
       </c>
-      <c r="F14" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="G14" s="5" t="n">
+      <c r="F14" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G14" s="6" t="n">
         <v>44567</v>
       </c>
-      <c r="H14" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="I14" s="5" t="n">
+      <c r="H14" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I14" s="6" t="n">
         <v>44932</v>
       </c>
-      <c r="J14" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="K14" s="5" t="n">
+      <c r="J14" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K14" s="6" t="n">
         <v>45297</v>
       </c>
-      <c r="L14" s="0" t="s">
+      <c r="L14" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
+      <c r="A15" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="0" t="str">
-        <f aca="false">IF($C$3&lt;$E17,"C74",IF($C$3&lt;$G17,"C75",IF($C$3&lt;$I17,"C76",IF($C$3&lt;$K17,"C77","C78"))))</f>
-        <v>C78</v>
-      </c>
-      <c r="D15" s="5" t="n">
+      <c r="B15" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15" s="6" t="n">
         <v>44012</v>
       </c>
-      <c r="E15" s="5" t="n">
+      <c r="E15" s="6" t="n">
         <v>44377</v>
       </c>
-      <c r="F15" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="G15" s="5" t="n">
+      <c r="F15" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G15" s="6" t="n">
         <v>44742</v>
       </c>
-      <c r="H15" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="I15" s="5" t="n">
+      <c r="H15" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I15" s="6" t="n">
         <v>45107</v>
       </c>
-      <c r="J15" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="K15" s="5" t="n">
+      <c r="J15" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K15" s="6" t="n">
         <v>45473</v>
       </c>
-      <c r="L15" s="0" t="s">
+      <c r="L15" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
+      <c r="A16" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B16" s="0" t="str">
-        <f aca="false">IF($C$3&lt;$E18,"C74",IF($C$3&lt;$G18,"C75",IF($C$3&lt;$I18,"C76",IF($C$3&lt;$K18,"C77","C78"))))</f>
-        <v>C78</v>
-      </c>
-      <c r="D16" s="5" t="n">
+      <c r="B16" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D16" s="6" t="n">
         <v>44312</v>
       </c>
-      <c r="E16" s="5" t="n">
+      <c r="E16" s="6" t="n">
         <v>44677</v>
       </c>
-      <c r="F16" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="G16" s="5" t="n">
+      <c r="F16" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G16" s="6" t="n">
         <v>45042</v>
       </c>
-      <c r="H16" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="I16" s="5" t="n">
+      <c r="H16" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I16" s="6" t="n">
         <v>45408</v>
       </c>
-      <c r="J16" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="K16" s="5" t="n">
+      <c r="J16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K16" s="6" t="n">
         <v>45773</v>
       </c>
-      <c r="L16" s="0" t="s">
+      <c r="L16" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
+      <c r="A17" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B17" s="0" t="str">
-        <f aca="false">IF($C$3&lt;$E19,"C74",IF($C$3&lt;$G19,"C75",IF($C$3&lt;$I19,"C76",IF($C$3&lt;$K19,"C77","C78"))))</f>
-        <v>C78</v>
-      </c>
-      <c r="D17" s="5" t="n">
+      <c r="B17" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D17" s="6" t="n">
         <v>44340</v>
       </c>
-      <c r="E17" s="5" t="n">
+      <c r="E17" s="6" t="n">
         <v>44705</v>
       </c>
-      <c r="F17" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="G17" s="5" t="n">
+      <c r="F17" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G17" s="6" t="n">
         <v>45070</v>
       </c>
-      <c r="H17" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="I17" s="5" t="n">
+      <c r="H17" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I17" s="6" t="n">
         <v>45436</v>
       </c>
-      <c r="J17" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="K17" s="5" t="n">
+      <c r="J17" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K17" s="6" t="n">
         <v>45801</v>
       </c>
-      <c r="L17" s="0" t="s">
+      <c r="L17" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
+      <c r="A18" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D18" s="5" t="n">
+      <c r="D18" s="6" t="n">
         <v>44348</v>
       </c>
-      <c r="E18" s="5" t="n">
+      <c r="E18" s="6" t="n">
         <v>44713</v>
       </c>
-      <c r="F18" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="G18" s="5" t="n">
+      <c r="F18" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G18" s="6" t="n">
         <v>45078</v>
       </c>
-      <c r="H18" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="I18" s="5" t="n">
+      <c r="H18" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I18" s="6" t="n">
         <v>45444</v>
       </c>
-      <c r="J18" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="K18" s="5" t="n">
+      <c r="J18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K18" s="6" t="n">
         <v>45809</v>
       </c>
-      <c r="L18" s="0" t="s">
+      <c r="L18" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
+      <c r="A19" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="5" t="n">
+      <c r="D19" s="6" t="n">
         <v>44455</v>
       </c>
-      <c r="E19" s="5" t="n">
+      <c r="E19" s="6" t="n">
         <v>44820</v>
       </c>
-      <c r="F19" s="0" t="s">
-        <v>4</v>
-      </c>
-      <c r="G19" s="5" t="n">
+      <c r="F19" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G19" s="6" t="n">
         <v>45185</v>
       </c>
-      <c r="H19" s="0" t="s">
-        <v>6</v>
-      </c>
-      <c r="I19" s="5" t="n">
+      <c r="H19" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I19" s="6" t="n">
         <v>45551</v>
       </c>
-      <c r="J19" s="0" t="s">
-        <v>7</v>
-      </c>
-      <c r="K19" s="5" t="n">
+      <c r="J19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K19" s="6" t="n">
         <v>45916</v>
       </c>
-      <c r="L19" s="0" t="s">
+      <c r="L19" s="1" t="s">
         <v>8</v>
       </c>
     </row>

--- a/outputs/32023.xlsx
+++ b/outputs/32023.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="32">
   <si>
     <t xml:space="preserve">Employee Name</t>
   </si>
@@ -560,9 +560,6 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="D2" s="2" t="s">
         <v>9</v>
       </c>
@@ -592,9 +589,6 @@
       </c>
     </row>
     <row r="3" customFormat="false" ht="28.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="1" t="s">
-        <v>8</v>
-      </c>
       <c r="C3" s="6" t="n">
         <f aca="true">TODAY()</f>
         <v>46271</v>
@@ -629,8 +623,9 @@
       <c r="A4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>8</v>
+      <c r="B4" s="6" t="n">
+        <f aca="false">IF($C$3&gt;=$D4,$E4,$G4)</f>
+        <v>42498</v>
       </c>
       <c r="D4" s="6" t="n">
         <v>42132</v>
@@ -664,8 +659,9 @@
       <c r="A5" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>8</v>
+      <c r="B5" s="6" t="n">
+        <f aca="false">IF($C$3&gt;=$D5,$E5,$G5)</f>
+        <v>42509</v>
       </c>
       <c r="D5" s="6" t="n">
         <v>42143</v>
@@ -699,8 +695,9 @@
       <c r="A6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>8</v>
+      <c r="B6" s="6" t="n">
+        <f aca="false">IF($C$3&gt;=$D6,$E6,$G6)</f>
+        <v>42560</v>
       </c>
       <c r="D6" s="6" t="n">
         <v>42194</v>
@@ -734,8 +731,9 @@
       <c r="A7" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>8</v>
+      <c r="B7" s="6" t="n">
+        <f aca="false">IF($C$3&gt;=$D7,$E7,$G7)</f>
+        <v>42682</v>
       </c>
       <c r="D7" s="6" t="n">
         <v>42316</v>
@@ -769,8 +767,9 @@
       <c r="A8" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>8</v>
+      <c r="B8" s="6" t="n">
+        <f aca="false">IF($C$3&gt;=$D8,$E8,$G8)</f>
+        <v>42989</v>
       </c>
       <c r="D8" s="6" t="n">
         <v>42624</v>
@@ -804,8 +803,9 @@
       <c r="A9" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>8</v>
+      <c r="B9" s="6" t="n">
+        <f aca="false">IF($C$3&gt;=$D9,$E9,$G9)</f>
+        <v>42989</v>
       </c>
       <c r="D9" s="6" t="n">
         <v>42624</v>
@@ -839,8 +839,9 @@
       <c r="A10" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>8</v>
+      <c r="B10" s="6" t="n">
+        <f aca="false">IF($C$3&gt;=$D10,$E10,$G10)</f>
+        <v>43087</v>
       </c>
       <c r="D10" s="6" t="n">
         <v>42722</v>
@@ -874,8 +875,9 @@
       <c r="A11" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>8</v>
+      <c r="B11" s="6" t="n">
+        <f aca="false">IF($C$3&gt;=$D11,$E11,$G11)</f>
+        <v>42989</v>
       </c>
       <c r="D11" s="6" t="n">
         <v>42624</v>
@@ -909,8 +911,9 @@
       <c r="A12" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>7</v>
+      <c r="B12" s="6" t="n">
+        <f aca="false">IF($C$3&gt;=$D12,$E12,$G12)</f>
+        <v>43087</v>
       </c>
       <c r="D12" s="6" t="n">
         <v>42722</v>
@@ -944,8 +947,9 @@
       <c r="A13" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>7</v>
+      <c r="B13" s="6" t="n">
+        <f aca="false">IF($C$3&gt;=$D13,$E13,$G13)</f>
+        <v>44075</v>
       </c>
       <c r="D13" s="6" t="n">
         <v>43709</v>
@@ -979,8 +983,9 @@
       <c r="A14" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>6</v>
+      <c r="B14" s="6" t="n">
+        <f aca="false">IF($C$3&gt;=$D14,$E14,$G14)</f>
+        <v>44202</v>
       </c>
       <c r="D14" s="6" t="n">
         <v>43836</v>
@@ -1014,8 +1019,9 @@
       <c r="A15" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>6</v>
+      <c r="B15" s="6" t="n">
+        <f aca="false">IF($C$3&gt;=$D15,$E15,$G15)</f>
+        <v>44377</v>
       </c>
       <c r="D15" s="6" t="n">
         <v>44012</v>
@@ -1049,8 +1055,9 @@
       <c r="A16" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>6</v>
+      <c r="B16" s="6" t="n">
+        <f aca="false">IF($C$3&gt;=$D16,$E16,$G16)</f>
+        <v>44677</v>
       </c>
       <c r="D16" s="6" t="n">
         <v>44312</v>
@@ -1084,8 +1091,9 @@
       <c r="A17" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>6</v>
+      <c r="B17" s="6" t="n">
+        <f aca="false">IF($C$3&gt;=$D17,$E17,$G17)</f>
+        <v>44705</v>
       </c>
       <c r="D17" s="6" t="n">
         <v>44340</v>
@@ -1119,6 +1127,10 @@
       <c r="A18" s="1" t="s">
         <v>30</v>
       </c>
+      <c r="B18" s="6" t="n">
+        <f aca="false">IF($C$3&gt;=$D18,$E18,$G18)</f>
+        <v>44713</v>
+      </c>
       <c r="D18" s="6" t="n">
         <v>44348</v>
       </c>
@@ -1150,6 +1162,10 @@
     <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
         <v>31</v>
+      </c>
+      <c r="B19" s="6" t="n">
+        <f aca="false">IF($C$3&gt;=$D19,$E19,$G19)</f>
+        <v>44820</v>
       </c>
       <c r="D19" s="6" t="n">
         <v>44455</v>
